--- a/Cardiologie/Excel/cardio_2.xlsx
+++ b/Cardiologie/Excel/cardio_2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\moito\Desktop\Sérieux\Projet\Site web\Cardiologie\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\Haris\Site-Web\Cardiologie\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBF8B9E3-8B5A-4608-8A69-F18C779245A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFCB536A-0C56-4DDA-9E2C-328F6ED5CDEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="211">
   <si>
     <t>L'hypertension artérielle est essentielle chez 95 % des patients hypertendus.</t>
   </si>
@@ -34,9 +34,6 @@
     <t>L'activation orthosympathique est généralement présente chez les sujets hypertendus de plus de 40 ans.</t>
   </si>
   <si>
-    <t>Les effets de l'angiotensine II dans l’hypertension sont exclusivement médiés par les récepteurs AT</t>
-  </si>
-  <si>
     <t>Les antagonistes de l'angiotensine II sont contre-indiqués si le patient a une insuffisance rénale aiguë.</t>
   </si>
   <si>
@@ -55,9 +52,6 @@
     <t>Les diurétiques sont à éviter en cas de décompensation cardiaque.</t>
   </si>
   <si>
-    <t>Les bêta-bloquants à haute dose sont contre-indiqués chez les patients présentant une insuffisance cardiaque.</t>
-  </si>
-  <si>
     <t>Les inhibiteurs de l'enzyme de conversion et les sartans sont contre-indiqués chez les femmes enceintes.</t>
   </si>
   <si>
@@ -112,18 +106,12 @@
     <t>Le traitement pharmacologique de l'HTA doit être ajusté en fonction du risque cardiovasculaire.</t>
   </si>
   <si>
-    <t>Une réduction de 10 mmHg de la PAS et de 5 mmHg de la PAD diminue les événements coronaires de 15 %.</t>
-  </si>
-  <si>
     <t>Les inhibiteurs de l'enzyme de conversion sont associés aux antagonistes de l’angiotensine II uniquement en cas d’HTA sévère (grade 3).</t>
   </si>
   <si>
     <t>L'HTA diastolique isolée est plus fréquente après l'âge de 60 ans.</t>
   </si>
   <si>
-    <t>Une réduction de 10 mmHg de la PAS et de 5 mmHg de la PAD diminue les AVC de 25 %.</t>
-  </si>
-  <si>
     <t>Le traitement pharmacologique de l'HTA est toujours nécessaire même si les mesures non pharmacologiques sont efficaces.</t>
   </si>
   <si>
@@ -292,9 +280,6 @@
     <t>Les contraceptifs oraux peuvent causer une hypertension.</t>
   </si>
   <si>
-    <t>La mesure de la tension se fait sur le bras pendant pour éviter toute contraction musculaire.</t>
-  </si>
-  <si>
     <t>Un taux de potassium inférieur à 3.5 meq/l sans diurétiques peut indiquer un hyperaldostéronisme.</t>
   </si>
   <si>
@@ -527,6 +512,147 @@
   </si>
   <si>
     <t>La correction de la sténose des artères rénales n’améliore pas VRAIment la pression artérielle.</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>En l'absence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inférieur à </t>
+  </si>
+  <si>
+    <t>De moins de 40 ans</t>
+  </si>
+  <si>
+    <t>Les effets de l'angiotensine II dans l’hypertension sont exclusivement médiés par les récepteurs AT1</t>
+  </si>
+  <si>
+    <t>Non ils sont aussi médiée par les récepteurs AT2</t>
+  </si>
+  <si>
+    <t>Chez l'homme de plus de 50 ans</t>
+  </si>
+  <si>
+    <t>Non c'est pour la dysplasie fibromusculaire</t>
+  </si>
+  <si>
+    <t>Non ils sont à conseiller</t>
+  </si>
+  <si>
+    <t>Non c'est fréquent</t>
+  </si>
+  <si>
+    <t>Antimitotique et antiproliférative</t>
+  </si>
+  <si>
+    <t>que si le risque est élevé</t>
+  </si>
+  <si>
+    <t>C'est l'inverse (faut se dire que le cerveau c tjr super risqué à haute tension et le cœur moins donc quand tu réduis, t'y gagnes plus vis-à-vis du cerveau que vis-à-vis du cœur)</t>
+  </si>
+  <si>
+    <t>C'est en seconde intention (voir cours de pharmaco)</t>
+  </si>
+  <si>
+    <t>pas rarement</t>
+  </si>
+  <si>
+    <t>à l'hopital aux soins intensifs</t>
+  </si>
+  <si>
+    <t>C'est de grade 3</t>
+  </si>
+  <si>
+    <t>faut jamais les associer zbi</t>
+  </si>
+  <si>
+    <t>C'est HTA systolique</t>
+  </si>
+  <si>
+    <t>Non que si ça marche pas les mesures non pharmaco</t>
+  </si>
+  <si>
+    <t>c'est que moins de 5%</t>
+  </si>
+  <si>
+    <t>c'est multifactorielle</t>
+  </si>
+  <si>
+    <t>aussi de la précharge</t>
+  </si>
+  <si>
+    <t>ça dépend du récepteur</t>
+  </si>
+  <si>
+    <t>Sont bas</t>
+  </si>
+  <si>
+    <t>La vasoconstriction</t>
+  </si>
+  <si>
+    <t>pauvre en potassium</t>
+  </si>
+  <si>
+    <t>ça a un effet</t>
+  </si>
+  <si>
+    <t>augmente</t>
+  </si>
+  <si>
+    <t>20 à 40%</t>
+  </si>
+  <si>
+    <t>25% des adultes</t>
+  </si>
+  <si>
+    <t>rappel de physiopat</t>
+  </si>
+  <si>
+    <t>nan ils sont normaux</t>
+  </si>
+  <si>
+    <t>résiste à un IEC ou sartans (logique ça touche le rein)</t>
+  </si>
+  <si>
+    <t>non c'est à bannir</t>
+  </si>
+  <si>
+    <t>non ça expose pas</t>
+  </si>
+  <si>
+    <t>c'est une minorité</t>
+  </si>
+  <si>
+    <t>3eme cause de décès</t>
+  </si>
+  <si>
+    <t>arbitraire</t>
+  </si>
+  <si>
+    <t>(PAS 160-179 et/ou PAD 100-109 mmHg)</t>
+  </si>
+  <si>
+    <t>plus de 60 ans</t>
+  </si>
+  <si>
+    <t>c faux wsh</t>
+  </si>
+  <si>
+    <t>fou rire j'avais meme pas remarqué l'appellation</t>
+  </si>
+  <si>
+    <t>30min</t>
+  </si>
+  <si>
+    <t>non le contraire</t>
+  </si>
+  <si>
+    <t>non à la PAD</t>
+  </si>
+  <si>
+    <t>un taux faible</t>
   </si>
 </sst>
 </file>
@@ -562,13 +688,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -874,38 +1003,39 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G163"/>
+  <dimension ref="A1:G159"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="174.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="9.140625" style="1"/>
+    <col min="2" max="2" width="117.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9" style="1" customWidth="1"/>
+    <col min="4" max="4" width="46.28515625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="9.140625" style="1"/>
     <col min="6" max="7" width="8" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>166</v>
-      </c>
       <c r="E1" s="2" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="30" x14ac:dyDescent="0.25">
@@ -913,10 +1043,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="C2" s="1" t="b">
         <v>0</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -929,6 +1068,12 @@
       <c r="C3" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="E3" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>164</v>
+      </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
@@ -940,6 +1085,12 @@
       <c r="C4" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="E4" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>164</v>
+      </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
@@ -951,6 +1102,15 @@
       <c r="C5" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="D5" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>164</v>
+      </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
@@ -962,16 +1122,34 @@
       <c r="C6" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="D6" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>164</v>
+      </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>4</v>
+        <v>168</v>
       </c>
       <c r="C7" s="1" t="b">
         <v>0</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -979,10 +1157,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C8" s="1" t="b">
         <v>1</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -990,10 +1174,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C9" s="1" t="b">
         <v>1</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -1001,10 +1191,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C10" s="1" t="b">
         <v>0</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -1012,10 +1211,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C11" s="1" t="b">
         <v>1</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -1023,10 +1228,19 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C12" s="1" t="b">
         <v>0</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -1034,10 +1248,19 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C13" s="1" t="b">
         <v>0</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -1045,10 +1268,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C14" s="1" t="b">
         <v>1</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -1056,1638 +1285,2578 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C15" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C16" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C17" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E17" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C18" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C19" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C20" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E20" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C21" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C22" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C23" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C24" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D24" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C25" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C26" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C27" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D27" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C28" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C29" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E29" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C30" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C31" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C32" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>32</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C33" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>33</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C34" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D34" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>34</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C35" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>35</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C36" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D36" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>36</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C37" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D37" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>37</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C38" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E38" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>38</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C39" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D39" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>39</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C40" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>40</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C41" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>41</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C42" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>42</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C43" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E43" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>43</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C44" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D44" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>44</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C45" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>45</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C46" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E46" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>46</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C47" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D47" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>47</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C48" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D48" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>48</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C49" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>49</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C50" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>50</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C51" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>51</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C52" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>52</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C53" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>53</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C54" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>54</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C55" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D55" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>55</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C56" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>56</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C57" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>57</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>55</v>
+        <v>163</v>
       </c>
       <c r="C58" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E58" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>58</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C59" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E59" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>59</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C60" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>60</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>168</v>
+        <v>56</v>
       </c>
       <c r="C61" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E61" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>61</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C62" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E62" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>62</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C63" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D63" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>63</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C64" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E64" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>64</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C65" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>65</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C66" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>66</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C67" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E67" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>67</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C68" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>68</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C69" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E69" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <v>69</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C70" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E70" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>70</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C71" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>71</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C72" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <v>72</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C73" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <v>73</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C74" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <v>74</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C75" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <v>75</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C76" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D76" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>76</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C77" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>77</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C78" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
         <v>78</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C79" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D79" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
         <v>79</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C80" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
         <v>80</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C81" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D81" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
         <v>81</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C82" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
         <v>82</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C83" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E83" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
         <v>83</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C84" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
         <v>84</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C85" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
         <v>85</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C86" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
         <v>86</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C87" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E87" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
         <v>87</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C88" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D88" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
         <v>88</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C89" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
         <v>89</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C90" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E90" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
         <v>90</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C91" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
         <v>91</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C92" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E92" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
         <v>92</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C93" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
         <v>93</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C94" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
         <v>94</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C95" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E95" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
         <v>95</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C96" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E96" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
         <v>96</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C97" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
         <v>97</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C98" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
         <v>98</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C99" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E99" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
         <v>99</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C100" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E100" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
         <v>100</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C101" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E101" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
         <v>101</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C102" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E102" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F102" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
         <v>102</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C103" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E103" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F103" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
         <v>103</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C104" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="E104" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F104" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
         <v>104</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C105" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E105" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F105" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
         <v>105</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C106" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E106" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F106" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
         <v>106</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C107" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E107" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F107" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
         <v>107</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C108" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E108" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F108" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
         <v>108</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C109" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="E109" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F109" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
         <v>109</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C110" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="E110" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F110" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
         <v>110</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C111" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E111" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F111" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
         <v>111</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C112" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="E112" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F112" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
         <v>112</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C113" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E113" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F113" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
         <v>113</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C114" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E114" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F114" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
         <v>114</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C115" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E115" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F115" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
         <v>115</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C116" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E116" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F116" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
         <v>116</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C117" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="E117" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F117" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
         <v>117</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C118" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E118" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F118" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
         <v>118</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C119" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="E119" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F119" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
         <v>119</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C120" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="E120" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F120" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
         <v>120</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C121" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="E121" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F121" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
         <v>121</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C122" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E122" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F122" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
         <v>122</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C123" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="E123" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F123" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
         <v>123</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C124" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="E124" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F124" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
         <v>124</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C125" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E125" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F125" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
         <v>125</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C126" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E126" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F126" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1">
         <v>126</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C127" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E127" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F127" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
         <v>127</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C128" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E128" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F128" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1">
         <v>128</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C129" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="E129" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F129" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1">
         <v>129</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C130" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="E130" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F130" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A131" s="1">
         <v>130</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C131" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E131" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F131" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1">
         <v>131</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C132" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="E132" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F132" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A133" s="1">
         <v>132</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C133" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E133" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F133" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="1">
         <v>133</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C134" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E134" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F134" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1">
         <v>134</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C135" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="E135" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F135" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1">
         <v>135</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C136" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="E136" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F136" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1">
         <v>136</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C137" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="E137" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F137" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="1">
         <v>137</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C138" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E138" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F138" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1">
         <v>138</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C139" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E139" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F139" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1">
         <v>139</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C140" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="E140" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F140" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="1">
         <v>140</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C141" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="E141" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F141" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="1">
         <v>141</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C142" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E142" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F142" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="1">
         <v>142</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C143" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E143" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F143" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="1">
         <v>143</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C144" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="E144" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F144" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A145" s="1">
         <v>144</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C145" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E145" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F145" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1">
         <v>145</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C146" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E146" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F146" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="1">
         <v>146</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C147" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="E147" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F147" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1">
         <v>147</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C148" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E148" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F148" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="1">
         <v>148</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C149" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="E149" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F149" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="1">
         <v>149</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C150" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="E150" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F150" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="1">
         <v>150</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C151" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="E151" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F151" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="1">
         <v>151</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C152" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="E152" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F152" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="1">
         <v>152</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C153" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="E153" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F153" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="1">
         <v>153</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C154" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="E154" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F154" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="1">
         <v>154</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C155" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="E155" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F155" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="1">
         <v>155</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C156" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="E156" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F156" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="1">
         <v>156</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C157" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E157" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F157" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="1">
         <v>157</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C158" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E158" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F158" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="1">
         <v>158</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C159" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A160" s="1">
-        <v>159</v>
-      </c>
-      <c r="B160" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="C160" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A161" s="1">
-        <v>160</v>
-      </c>
-      <c r="B161" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="C161" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A162" s="1">
-        <v>161</v>
-      </c>
-      <c r="B162" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="C162" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A163" s="1">
-        <v>162</v>
-      </c>
-      <c r="B163" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="C163" s="1" t="b">
-        <v>1</v>
+      <c r="E159" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F159" s="1" t="s">
+        <v>164</v>
       </c>
     </row>
   </sheetData>

--- a/Cardiologie/Excel/cardio_2.xlsx
+++ b/Cardiologie/Excel/cardio_2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\Haris\Site-Web\Cardiologie\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\moito\Desktop\Sérieux\Projet\Site web\Cardiologie\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFCB536A-0C56-4DDA-9E2C-328F6ED5CDEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B494EF1-4A01-4F14-8014-24704D8408E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="270">
   <si>
     <t>L'hypertension artérielle est essentielle chez 95 % des patients hypertendus.</t>
   </si>
@@ -653,6 +653,183 @@
   </si>
   <si>
     <t>un taux faible</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La décision est basée sur le risque de décès cardiovasculaire à 10 ans </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le bénéfice augmente proportionnellement avec la durée du traitement </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'objectif tensionnel cible est une valeur inférieure à 140/90 mmHg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le traitement débute immédiatement si le risque cardiovasculaire est élevé ou très élevé </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Une monothérapie est privilégiée pour les patients de plus de 80 ans ou fragiles </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le texte recommande de privilégier les médicaments actifs durant 24 heures </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La monothérapie est le traitement initial recommandé pour un grade 1 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'adaptation du traitement est envisagée après 4 à 6 semaines (et non 2) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les diurétiques thiazidiques sont indiqués spécifiquement pour les patients âgés </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ces pathologies pulmonaires sont des contre-indications aux bêta-bloquants </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ils sont formellement à éviter en cas de décompensation cardiaque </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ils sont au contraire indiqués pour traiter la néphropathie diabétique </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ils sont indiqués en cas de résistance aux cinq classes thérapeutiques majeures </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le potassium est cité comme un facteur environnemental permettant de réduire la PA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le traitement combiné est la règle, sauf pour les grades 1 ou patients de &gt; 80 ans </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C'est l'indication principale de cette classe en cas d'effets secondaires aux IEC </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ils constituent le traitement de choix pour cette forme d'hypertension </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'hyperkaliémie est une contre-indication formelle à l'usage des IEC </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'association de ces deux classes thérapeutiques est formellement interdite </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'exercice physique régulier fait partie des mesures non pharmacologiques conseillées </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ils sont privilégiés spécifiquement en cas de décompensation cardiaque </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le texte confirme qu'ils doivent être évités en présence d'un bloc AV </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leur utilisation est recommandée pour cette pathologie cardiaque </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ils sont recommandés pour l'hypertension systolique isolée (et non diastolique) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document valide leur prescription suite à un infarctus myocardique </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ils sont à éviter car ils peuvent altérer les performances dynamiques </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ils sont spécifiquement recommandés pour cette complication du diabète </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leur usage est interdit pendant la grossesse en raison de ce risque </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ils sont au contraire à éviter formellement en cas de bloc AV </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C'est le mécanisme normal d'autorégulation lors d'une hausse modérée de la PA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'autorégulation est au contraire perdue lors d'élévations très importantes </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C'est la description de la cascade pathologique menant à la nécrose artériolaire </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'oedème cérébral est associé à une rupture de la barrière hémato-méningée </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les troubles visuels sont, avec les céphalées, les symptômes les plus fréquents </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ces manifestations cliniques caractérisent l'encéphalopathie hypertensive </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le traitement est purement médical (hypotenseurs en soins intensifs) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'urgence impose au contraire un traitement par voie intraveineuse </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le risque cardiovasculaire augmente de façon continue avec le niveau de pression </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La PA est le produit du débit cardiaque par la résistance périphérique </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'hyperactivité sympathique peut effectivement régresser avec l'âge </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ils détériorent la fonction rénale en cas de sténose bilatérale des artères rénales </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'histoire familiale n'est présente que chez 10 % des patients (1 sur 10) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les événements coronaires sont effectivement la première cause de décès liée à l'HTA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le seuil de diagnostic est fixé là où les bénéfices du traitement dépassent son coût </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le grade 1 commence à partir de 140/90 mmHg (135/85 est normal) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'inobservance et les traitements insuffisants expliquent le manque de contrôle </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ils constituent un facteur de risque propre, indépendamment des autres </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Une pression de 170/100 mmHg correspond aux critères du grade 2 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'HTA non traitée est une cause majeure d'insuffisance rénale </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'HTA augmente la post-charge (et non la précharge) menant à l'insuffisance </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ce phénomène concerne principalement les sujets âgés aux artères rigides </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ce sont les conditions de mesure rigoureuses préconisées pour le diagnostic </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle est au contraire décrite comme fréquente chez les patients Parkinsoniens </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ils sont listés comme des causes médicamenteuses potentielles d'HTA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sous diurétiques, le seuil de suspicion de cette pathologie est de 3.0 mEq/L </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ils sont cités parmi les causes médicamenteuses provoquant une HTA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">On associe un bloqueur du SRAA à un calcique OU à un diurétique </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle est le traitement de choix à ajouter en cas d'hypertension résistante </t>
+  </si>
+  <si>
+    <t>Page</t>
   </si>
 </sst>
 </file>
@@ -1003,19 +1180,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G159"/>
+  <dimension ref="A1:H159"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="117.42578125" style="1" customWidth="1"/>
     <col min="3" max="3" width="9" style="1" customWidth="1"/>
-    <col min="4" max="4" width="46.28515625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="9.140625" style="1"/>
-    <col min="6" max="7" width="8" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="46.28515625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" style="1"/>
+    <col min="7" max="8" width="8" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>156</v>
       </c>
@@ -1029,16 +1206,19 @@
         <v>161</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1051,14 +1231,14 @@
       <c r="D2" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F2" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G2" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1068,14 +1248,14 @@
       <c r="C3" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F3" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G3" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1085,14 +1265,14 @@
       <c r="C4" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F4" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G4" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1105,14 +1285,14 @@
       <c r="D5" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F5" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G5" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1125,14 +1305,14 @@
       <c r="D6" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F6" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G6" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -1145,14 +1325,14 @@
       <c r="D7" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F7" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G7" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -1162,14 +1342,14 @@
       <c r="C8" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="E8" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F8" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G8" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -1179,14 +1359,14 @@
       <c r="C9" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="E9" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F9" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G9" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -1199,14 +1379,14 @@
       <c r="D10" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="E10" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F10" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G10" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -1216,14 +1396,14 @@
       <c r="C11" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="E11" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F11" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G11" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -1236,14 +1416,14 @@
       <c r="D12" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="E12" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F12" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G12" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -1256,14 +1436,14 @@
       <c r="D13" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="E13" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F13" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G13" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -1273,14 +1453,14 @@
       <c r="C14" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="E14" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F14" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G14" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -1293,14 +1473,14 @@
       <c r="D15" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="E15" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F15" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="G15" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -1310,14 +1490,14 @@
       <c r="C16" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="E16" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F16" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G16" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -1327,14 +1507,14 @@
       <c r="C17" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="E17" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F17" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G17" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -1347,14 +1527,14 @@
       <c r="D18" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="E18" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F18" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G18" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -1364,14 +1544,14 @@
       <c r="C19" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="E19" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F19" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G19" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -1381,14 +1561,14 @@
       <c r="C20" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="E20" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F20" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="G20" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -1401,14 +1581,14 @@
       <c r="D21" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="E21" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F21" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G21" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -1418,14 +1598,14 @@
       <c r="C22" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="E22" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F22" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="G22" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -1438,14 +1618,14 @@
       <c r="D23" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="E23" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F23" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="G23" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -1458,14 +1638,14 @@
       <c r="D24" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="E24" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F24" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G24" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -1475,14 +1655,14 @@
       <c r="C25" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="E25" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F25" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G25" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -1495,14 +1675,14 @@
       <c r="D26" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="E26" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F26" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G26" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>26</v>
       </c>
@@ -1515,14 +1695,14 @@
       <c r="D27" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="E27" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F27" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G27" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>27</v>
       </c>
@@ -1532,14 +1712,14 @@
       <c r="C28" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="E28" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F28" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G28" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>28</v>
       </c>
@@ -1549,14 +1729,14 @@
       <c r="C29" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="E29" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F29" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G29" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>29</v>
       </c>
@@ -1569,14 +1749,14 @@
       <c r="D30" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="E30" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F30" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G30" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>30</v>
       </c>
@@ -1586,14 +1766,14 @@
       <c r="C31" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="E31" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F31" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="32" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="G31" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>31</v>
       </c>
@@ -1606,14 +1786,14 @@
       <c r="D32" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="E32" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F32" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G32" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>32</v>
       </c>
@@ -1626,14 +1806,14 @@
       <c r="D33" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="E33" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F33" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="34" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="G33" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>33</v>
       </c>
@@ -1646,14 +1826,14 @@
       <c r="D34" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="E34" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F34" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G34" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>34</v>
       </c>
@@ -1663,14 +1843,14 @@
       <c r="C35" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="E35" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F35" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G35" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>35</v>
       </c>
@@ -1683,14 +1863,15 @@
       <c r="D36" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="E36" s="1" t="s">
-        <v>164</v>
-      </c>
+      <c r="E36" s="3"/>
       <c r="F36" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G36" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>36</v>
       </c>
@@ -1703,14 +1884,14 @@
       <c r="D37" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="E37" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F37" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G37" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>37</v>
       </c>
@@ -1720,14 +1901,14 @@
       <c r="C38" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="E38" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F38" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G38" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>38</v>
       </c>
@@ -1740,14 +1921,14 @@
       <c r="D39" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="E39" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F39" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G39" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>39</v>
       </c>
@@ -1757,14 +1938,14 @@
       <c r="C40" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="E40" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F40" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G40" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>40</v>
       </c>
@@ -1777,14 +1958,14 @@
       <c r="D41" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="E41" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F41" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G41" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>41</v>
       </c>
@@ -1794,14 +1975,14 @@
       <c r="C42" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="E42" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F42" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G42" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>42</v>
       </c>
@@ -1811,14 +1992,14 @@
       <c r="C43" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="E43" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F43" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G43" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>43</v>
       </c>
@@ -1831,14 +2012,14 @@
       <c r="D44" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="E44" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F44" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G44" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>44</v>
       </c>
@@ -1851,14 +2032,14 @@
       <c r="D45" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="E45" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F45" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G45" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>45</v>
       </c>
@@ -1868,14 +2049,14 @@
       <c r="C46" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="E46" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F46" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G46" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>46</v>
       </c>
@@ -1888,14 +2069,14 @@
       <c r="D47" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="E47" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F47" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G47" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>47</v>
       </c>
@@ -1908,14 +2089,14 @@
       <c r="D48" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="E48" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F48" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G48" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>48</v>
       </c>
@@ -1928,14 +2109,14 @@
       <c r="D49" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="E49" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F49" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G49" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>49</v>
       </c>
@@ -1945,14 +2126,14 @@
       <c r="C50" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="E50" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F50" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G50" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>50</v>
       </c>
@@ -1962,14 +2143,14 @@
       <c r="C51" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="E51" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F51" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G51" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>51</v>
       </c>
@@ -1979,14 +2160,14 @@
       <c r="C52" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="E52" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F52" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G52" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>52</v>
       </c>
@@ -1999,14 +2180,14 @@
       <c r="D53" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="E53" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F53" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G53" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>53</v>
       </c>
@@ -2019,14 +2200,14 @@
       <c r="D54" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="E54" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F54" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G54" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>54</v>
       </c>
@@ -2039,14 +2220,14 @@
       <c r="D55" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="E55" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F55" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G55" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>55</v>
       </c>
@@ -2056,14 +2237,14 @@
       <c r="C56" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="E56" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F56" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="57" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="G56" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>56</v>
       </c>
@@ -2073,14 +2254,14 @@
       <c r="C57" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="E57" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F57" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G57" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>57</v>
       </c>
@@ -2090,14 +2271,14 @@
       <c r="C58" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="E58" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F58" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G58" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>58</v>
       </c>
@@ -2107,14 +2288,14 @@
       <c r="C59" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="E59" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F59" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G59" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>59</v>
       </c>
@@ -2124,14 +2305,14 @@
       <c r="C60" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="E60" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F60" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="61" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="G60" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>60</v>
       </c>
@@ -2141,14 +2322,14 @@
       <c r="C61" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="E61" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F61" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="62" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="G61" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>61</v>
       </c>
@@ -2158,14 +2339,14 @@
       <c r="C62" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="E62" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F62" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G62" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>62</v>
       </c>
@@ -2178,14 +2359,14 @@
       <c r="D63" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="E63" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F63" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="64" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="G63" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>63</v>
       </c>
@@ -2195,14 +2376,14 @@
       <c r="C64" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="E64" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F64" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="65" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="G64" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>64</v>
       </c>
@@ -2215,14 +2396,14 @@
       <c r="D65" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="E65" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F65" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="66" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="G65" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>65</v>
       </c>
@@ -2232,14 +2413,14 @@
       <c r="C66" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="E66" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F66" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G66" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>66</v>
       </c>
@@ -2249,14 +2430,14 @@
       <c r="C67" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="E67" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F67" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="68" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="G67" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>67</v>
       </c>
@@ -2266,14 +2447,14 @@
       <c r="C68" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="E68" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F68" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G68" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>68</v>
       </c>
@@ -2283,14 +2464,14 @@
       <c r="C69" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="E69" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F69" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="70" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="G69" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <v>69</v>
       </c>
@@ -2300,14 +2481,14 @@
       <c r="C70" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="E70" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F70" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G70" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>70</v>
       </c>
@@ -2320,14 +2501,14 @@
       <c r="D71" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="E71" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F71" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="72" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="G71" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>71</v>
       </c>
@@ -2340,14 +2521,14 @@
       <c r="D72" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="E72" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F72" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G72" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <v>72</v>
       </c>
@@ -2360,14 +2541,14 @@
       <c r="D73" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="E73" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F73" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G73" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <v>73</v>
       </c>
@@ -2377,14 +2558,14 @@
       <c r="C74" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="E74" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F74" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G74" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <v>74</v>
       </c>
@@ -2394,14 +2575,14 @@
       <c r="C75" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="E75" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F75" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G75" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <v>75</v>
       </c>
@@ -2414,14 +2595,14 @@
       <c r="D76" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="E76" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F76" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G76" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>76</v>
       </c>
@@ -2434,14 +2615,14 @@
       <c r="D77" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="E77" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F77" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G77" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>77</v>
       </c>
@@ -2454,14 +2635,14 @@
       <c r="D78" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="E78" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F78" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G78" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
         <v>78</v>
       </c>
@@ -2474,14 +2655,14 @@
       <c r="D79" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="E79" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F79" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G79" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
         <v>79</v>
       </c>
@@ -2491,14 +2672,14 @@
       <c r="C80" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="E80" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F80" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G80" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
         <v>80</v>
       </c>
@@ -2511,14 +2692,14 @@
       <c r="D81" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="E81" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F81" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G81" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
         <v>81</v>
       </c>
@@ -2531,14 +2712,14 @@
       <c r="D82" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="E82" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F82" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G82" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
         <v>82</v>
       </c>
@@ -2548,14 +2729,14 @@
       <c r="C83" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="E83" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F83" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G83" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
         <v>83</v>
       </c>
@@ -2565,14 +2746,14 @@
       <c r="C84" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="E84" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F84" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G84" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
         <v>84</v>
       </c>
@@ -2585,14 +2766,14 @@
       <c r="D85" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="E85" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F85" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G85" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
         <v>85</v>
       </c>
@@ -2605,14 +2786,14 @@
       <c r="D86" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="E86" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F86" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G86" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
         <v>86</v>
       </c>
@@ -2622,14 +2803,14 @@
       <c r="C87" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="E87" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F87" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G87" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
         <v>87</v>
       </c>
@@ -2642,14 +2823,14 @@
       <c r="D88" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="E88" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F88" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G88" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
         <v>88</v>
       </c>
@@ -2659,14 +2840,14 @@
       <c r="C89" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="E89" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F89" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G89" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
         <v>89</v>
       </c>
@@ -2676,14 +2857,14 @@
       <c r="C90" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="E90" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F90" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G90" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
         <v>90</v>
       </c>
@@ -2693,14 +2874,14 @@
       <c r="C91" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="E91" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F91" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G91" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
         <v>91</v>
       </c>
@@ -2710,14 +2891,14 @@
       <c r="C92" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="E92" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F92" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="93" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="G92" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
         <v>92</v>
       </c>
@@ -2727,14 +2908,14 @@
       <c r="C93" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="E93" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F93" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G93" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
         <v>93</v>
       </c>
@@ -2744,14 +2925,14 @@
       <c r="C94" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="E94" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F94" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G94" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
         <v>94</v>
       </c>
@@ -2761,14 +2942,14 @@
       <c r="C95" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="E95" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F95" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G95" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
         <v>95</v>
       </c>
@@ -2778,14 +2959,14 @@
       <c r="C96" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="E96" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F96" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G96" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
         <v>96</v>
       </c>
@@ -2795,14 +2976,14 @@
       <c r="C97" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="E97" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F97" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G97" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
         <v>97</v>
       </c>
@@ -2815,14 +2996,14 @@
       <c r="D98" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="E98" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F98" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G98" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
         <v>98</v>
       </c>
@@ -2832,14 +3013,14 @@
       <c r="C99" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="E99" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F99" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G99" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
         <v>99</v>
       </c>
@@ -2849,14 +3030,14 @@
       <c r="C100" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="E100" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F100" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G100" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
         <v>100</v>
       </c>
@@ -2866,14 +3047,14 @@
       <c r="C101" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="E101" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F101" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G101" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
         <v>101</v>
       </c>
@@ -2883,14 +3064,20 @@
       <c r="C102" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="E102" s="1" t="s">
-        <v>164</v>
+      <c r="D102" t="s">
+        <v>211</v>
+      </c>
+      <c r="E102" s="1">
+        <v>6</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G102" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
         <v>102</v>
       </c>
@@ -2900,14 +3087,20 @@
       <c r="C103" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="E103" s="1" t="s">
-        <v>164</v>
+      <c r="D103" t="s">
+        <v>212</v>
+      </c>
+      <c r="E103" s="1">
+        <v>6</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G103" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
         <v>103</v>
       </c>
@@ -2917,14 +3110,20 @@
       <c r="C104" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="E104" s="1" t="s">
-        <v>164</v>
+      <c r="D104" t="s">
+        <v>213</v>
+      </c>
+      <c r="E104" s="1">
+        <v>6</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G104" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
         <v>104</v>
       </c>
@@ -2934,14 +3133,20 @@
       <c r="C105" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="E105" s="1" t="s">
-        <v>164</v>
+      <c r="D105" t="s">
+        <v>214</v>
+      </c>
+      <c r="E105" s="1">
+        <v>6</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G105" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
         <v>105</v>
       </c>
@@ -2951,14 +3156,20 @@
       <c r="C106" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="E106" s="1" t="s">
-        <v>164</v>
+      <c r="D106" t="s">
+        <v>215</v>
+      </c>
+      <c r="E106" s="1">
+        <v>6</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G106" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
         <v>106</v>
       </c>
@@ -2968,14 +3179,20 @@
       <c r="C107" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="E107" s="1" t="s">
-        <v>164</v>
+      <c r="D107" t="s">
+        <v>216</v>
+      </c>
+      <c r="E107" s="1">
+        <v>6</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G107" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
         <v>107</v>
       </c>
@@ -2985,14 +3202,20 @@
       <c r="C108" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="E108" s="1" t="s">
-        <v>164</v>
+      <c r="D108" t="s">
+        <v>217</v>
+      </c>
+      <c r="E108" s="1">
+        <v>6</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G108" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
         <v>108</v>
       </c>
@@ -3002,14 +3225,20 @@
       <c r="C109" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="E109" s="1" t="s">
-        <v>164</v>
+      <c r="D109" t="s">
+        <v>218</v>
+      </c>
+      <c r="E109" s="1">
+        <v>6</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G109" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
         <v>109</v>
       </c>
@@ -3019,14 +3248,20 @@
       <c r="C110" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="E110" s="1" t="s">
-        <v>164</v>
+      <c r="D110" t="s">
+        <v>219</v>
+      </c>
+      <c r="E110" s="1">
+        <v>7</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G110" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
         <v>110</v>
       </c>
@@ -3036,14 +3271,20 @@
       <c r="C111" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="E111" s="1" t="s">
-        <v>164</v>
+      <c r="D111" t="s">
+        <v>220</v>
+      </c>
+      <c r="E111" s="1">
+        <v>7</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G111" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
         <v>111</v>
       </c>
@@ -3053,14 +3294,20 @@
       <c r="C112" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="E112" s="1" t="s">
-        <v>164</v>
+      <c r="D112" t="s">
+        <v>221</v>
+      </c>
+      <c r="E112" s="1">
+        <v>7</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G112" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
         <v>112</v>
       </c>
@@ -3070,14 +3317,20 @@
       <c r="C113" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="E113" s="1" t="s">
-        <v>164</v>
+      <c r="D113" t="s">
+        <v>222</v>
+      </c>
+      <c r="E113" s="1">
+        <v>7</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G113" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
         <v>113</v>
       </c>
@@ -3087,14 +3340,20 @@
       <c r="C114" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="E114" s="1" t="s">
-        <v>164</v>
+      <c r="D114" t="s">
+        <v>223</v>
+      </c>
+      <c r="E114" s="1">
+        <v>7</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G114" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
         <v>114</v>
       </c>
@@ -3104,14 +3363,20 @@
       <c r="C115" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="E115" s="1" t="s">
-        <v>164</v>
+      <c r="D115" t="s">
+        <v>224</v>
+      </c>
+      <c r="E115" s="1">
+        <v>6</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G115" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
         <v>115</v>
       </c>
@@ -3121,14 +3386,20 @@
       <c r="C116" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="E116" s="1" t="s">
-        <v>164</v>
+      <c r="D116" t="s">
+        <v>225</v>
+      </c>
+      <c r="E116" s="1">
+        <v>6</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G116" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
         <v>116</v>
       </c>
@@ -3138,14 +3409,20 @@
       <c r="C117" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="E117" s="1" t="s">
-        <v>164</v>
+      <c r="D117" t="s">
+        <v>226</v>
+      </c>
+      <c r="E117" s="1">
+        <v>7</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G117" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
         <v>117</v>
       </c>
@@ -3155,14 +3432,20 @@
       <c r="C118" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="E118" s="1" t="s">
-        <v>164</v>
+      <c r="D118" t="s">
+        <v>227</v>
+      </c>
+      <c r="E118" s="1">
+        <v>7</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G118" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
         <v>118</v>
       </c>
@@ -3172,14 +3455,20 @@
       <c r="C119" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="E119" s="1" t="s">
-        <v>164</v>
+      <c r="D119" t="s">
+        <v>228</v>
+      </c>
+      <c r="E119" s="1">
+        <v>7</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G119" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
         <v>119</v>
       </c>
@@ -3189,14 +3478,20 @@
       <c r="C120" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="E120" s="1" t="s">
-        <v>164</v>
+      <c r="D120" t="s">
+        <v>229</v>
+      </c>
+      <c r="E120" s="1">
+        <v>7</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G120" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
         <v>120</v>
       </c>
@@ -3206,14 +3501,20 @@
       <c r="C121" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="E121" s="1" t="s">
-        <v>164</v>
+      <c r="D121" t="s">
+        <v>230</v>
+      </c>
+      <c r="E121" s="1">
+        <v>6</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G121" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
         <v>121</v>
       </c>
@@ -3223,14 +3524,20 @@
       <c r="C122" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="E122" s="1" t="s">
-        <v>164</v>
+      <c r="D122" t="s">
+        <v>231</v>
+      </c>
+      <c r="E122" s="1">
+        <v>7</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G122" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
         <v>122</v>
       </c>
@@ -3240,14 +3547,20 @@
       <c r="C123" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="E123" s="1" t="s">
-        <v>164</v>
+      <c r="D123" t="s">
+        <v>232</v>
+      </c>
+      <c r="E123" s="1">
+        <v>7</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G123" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
         <v>123</v>
       </c>
@@ -3257,14 +3570,20 @@
       <c r="C124" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="E124" s="1" t="s">
-        <v>164</v>
+      <c r="D124" t="s">
+        <v>233</v>
+      </c>
+      <c r="E124" s="1">
+        <v>7</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G124" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
         <v>124</v>
       </c>
@@ -3274,14 +3593,20 @@
       <c r="C125" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="E125" s="1" t="s">
-        <v>164</v>
+      <c r="D125" t="s">
+        <v>234</v>
+      </c>
+      <c r="E125" s="1">
+        <v>7</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G125" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
         <v>125</v>
       </c>
@@ -3291,14 +3616,20 @@
       <c r="C126" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="E126" s="1" t="s">
-        <v>164</v>
+      <c r="D126" t="s">
+        <v>235</v>
+      </c>
+      <c r="E126" s="1">
+        <v>7</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G126" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" s="1">
         <v>126</v>
       </c>
@@ -3308,14 +3639,20 @@
       <c r="C127" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="E127" s="1" t="s">
-        <v>164</v>
+      <c r="D127" t="s">
+        <v>236</v>
+      </c>
+      <c r="E127" s="1">
+        <v>7</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G127" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
         <v>127</v>
       </c>
@@ -3325,14 +3662,20 @@
       <c r="C128" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="E128" s="1" t="s">
-        <v>164</v>
+      <c r="D128" t="s">
+        <v>237</v>
+      </c>
+      <c r="E128" s="1">
+        <v>7</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G128" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" s="1">
         <v>128</v>
       </c>
@@ -3342,14 +3685,20 @@
       <c r="C129" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="E129" s="1" t="s">
-        <v>164</v>
+      <c r="D129" t="s">
+        <v>238</v>
+      </c>
+      <c r="E129" s="1">
+        <v>7</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G129" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" s="1">
         <v>129</v>
       </c>
@@ -3359,14 +3708,20 @@
       <c r="C130" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="E130" s="1" t="s">
-        <v>164</v>
+      <c r="D130" t="s">
+        <v>239</v>
+      </c>
+      <c r="E130" s="1">
+        <v>7</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="131" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="G130" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A131" s="1">
         <v>130</v>
       </c>
@@ -3376,14 +3731,20 @@
       <c r="C131" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="E131" s="1" t="s">
-        <v>164</v>
+      <c r="D131" t="s">
+        <v>240</v>
+      </c>
+      <c r="E131" s="1">
+        <v>7</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G131" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" s="1">
         <v>131</v>
       </c>
@@ -3393,14 +3754,20 @@
       <c r="C132" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="E132" s="1" t="s">
-        <v>164</v>
+      <c r="D132" t="s">
+        <v>241</v>
+      </c>
+      <c r="E132" s="1">
+        <v>7</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="133" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="G132" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A133" s="1">
         <v>132</v>
       </c>
@@ -3410,14 +3777,20 @@
       <c r="C133" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="E133" s="1" t="s">
-        <v>164</v>
+      <c r="D133" t="s">
+        <v>242</v>
+      </c>
+      <c r="E133" s="1">
+        <v>7</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G133" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" s="1">
         <v>133</v>
       </c>
@@ -3427,14 +3800,20 @@
       <c r="C134" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="E134" s="1" t="s">
-        <v>164</v>
+      <c r="D134" t="s">
+        <v>243</v>
+      </c>
+      <c r="E134" s="1">
+        <v>7</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G134" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" s="1">
         <v>134</v>
       </c>
@@ -3444,14 +3823,20 @@
       <c r="C135" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="E135" s="1" t="s">
-        <v>164</v>
+      <c r="D135" t="s">
+        <v>244</v>
+      </c>
+      <c r="E135" s="1">
+        <v>8</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G135" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136" s="1">
         <v>135</v>
       </c>
@@ -3461,14 +3846,20 @@
       <c r="C136" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="E136" s="1" t="s">
-        <v>164</v>
+      <c r="D136" t="s">
+        <v>245</v>
+      </c>
+      <c r="E136" s="1">
+        <v>8</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G136" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137" s="1">
         <v>136</v>
       </c>
@@ -3478,14 +3869,20 @@
       <c r="C137" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="E137" s="1" t="s">
-        <v>164</v>
+      <c r="D137" t="s">
+        <v>246</v>
+      </c>
+      <c r="E137" s="1">
+        <v>8</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G137" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138" s="1">
         <v>137</v>
       </c>
@@ -3495,14 +3892,20 @@
       <c r="C138" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="E138" s="1" t="s">
-        <v>164</v>
+      <c r="D138" t="s">
+        <v>247</v>
+      </c>
+      <c r="E138" s="1">
+        <v>8</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G138" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139" s="1">
         <v>138</v>
       </c>
@@ -3512,14 +3915,20 @@
       <c r="C139" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="E139" s="1" t="s">
-        <v>164</v>
+      <c r="D139" t="s">
+        <v>248</v>
+      </c>
+      <c r="E139" s="1">
+        <v>1</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G139" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140" s="1">
         <v>139</v>
       </c>
@@ -3529,14 +3938,20 @@
       <c r="C140" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="E140" s="1" t="s">
-        <v>164</v>
+      <c r="D140" t="s">
+        <v>249</v>
+      </c>
+      <c r="E140" s="1">
+        <v>1</v>
       </c>
       <c r="F140" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G140" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141" s="1">
         <v>140</v>
       </c>
@@ -3546,14 +3961,20 @@
       <c r="C141" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="E141" s="1" t="s">
-        <v>164</v>
+      <c r="D141" t="s">
+        <v>250</v>
+      </c>
+      <c r="E141" s="1">
+        <v>1</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G141" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142" s="1">
         <v>141</v>
       </c>
@@ -3563,14 +3984,20 @@
       <c r="C142" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="E142" s="1" t="s">
-        <v>164</v>
+      <c r="D142" t="s">
+        <v>251</v>
+      </c>
+      <c r="E142" s="1">
+        <v>2</v>
       </c>
       <c r="F142" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G142" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143" s="1">
         <v>142</v>
       </c>
@@ -3580,14 +4007,20 @@
       <c r="C143" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="E143" s="1" t="s">
-        <v>164</v>
+      <c r="D143" t="s">
+        <v>252</v>
+      </c>
+      <c r="E143" s="1">
+        <v>2</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G143" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144" s="1">
         <v>143</v>
       </c>
@@ -3597,14 +4030,20 @@
       <c r="C144" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="E144" s="1" t="s">
-        <v>164</v>
+      <c r="D144" t="s">
+        <v>253</v>
+      </c>
+      <c r="E144" s="1">
+        <v>3</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="145" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="G144" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A145" s="1">
         <v>144</v>
       </c>
@@ -3614,14 +4053,20 @@
       <c r="C145" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="E145" s="1" t="s">
-        <v>164</v>
+      <c r="D145" t="s">
+        <v>254</v>
+      </c>
+      <c r="E145" s="1">
+        <v>3</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G145" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A146" s="1">
         <v>145</v>
       </c>
@@ -3631,14 +4076,20 @@
       <c r="C146" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="E146" s="1" t="s">
-        <v>164</v>
+      <c r="D146" t="s">
+        <v>255</v>
+      </c>
+      <c r="E146" s="1">
+        <v>3</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G146" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A147" s="1">
         <v>146</v>
       </c>
@@ -3648,14 +4099,20 @@
       <c r="C147" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="E147" s="1" t="s">
-        <v>164</v>
+      <c r="D147" t="s">
+        <v>256</v>
+      </c>
+      <c r="E147" s="1">
+        <v>3</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G147" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A148" s="1">
         <v>147</v>
       </c>
@@ -3665,14 +4122,20 @@
       <c r="C148" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="E148" s="1" t="s">
-        <v>164</v>
+      <c r="D148" t="s">
+        <v>257</v>
+      </c>
+      <c r="E148" s="1">
+        <v>3</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G148" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A149" s="1">
         <v>148</v>
       </c>
@@ -3682,14 +4145,20 @@
       <c r="C149" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="E149" s="1" t="s">
-        <v>164</v>
+      <c r="D149" t="s">
+        <v>258</v>
+      </c>
+      <c r="E149" s="1">
+        <v>3</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G149" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A150" s="1">
         <v>149</v>
       </c>
@@ -3699,14 +4168,20 @@
       <c r="C150" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="E150" s="1" t="s">
-        <v>164</v>
+      <c r="D150" t="s">
+        <v>259</v>
+      </c>
+      <c r="E150" s="1">
+        <v>4</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G150" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A151" s="1">
         <v>150</v>
       </c>
@@ -3716,14 +4191,20 @@
       <c r="C151" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="E151" s="1" t="s">
-        <v>164</v>
+      <c r="D151" t="s">
+        <v>260</v>
+      </c>
+      <c r="E151" s="1">
+        <v>1</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G151" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A152" s="1">
         <v>151</v>
       </c>
@@ -3733,14 +4214,20 @@
       <c r="C152" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="E152" s="1" t="s">
-        <v>164</v>
+      <c r="D152" t="s">
+        <v>261</v>
+      </c>
+      <c r="E152" s="1">
+        <v>4</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G152" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A153" s="1">
         <v>152</v>
       </c>
@@ -3750,14 +4237,20 @@
       <c r="C153" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="E153" s="1" t="s">
-        <v>164</v>
+      <c r="D153" t="s">
+        <v>262</v>
+      </c>
+      <c r="E153" s="1">
+        <v>4</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G153" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A154" s="1">
         <v>153</v>
       </c>
@@ -3767,14 +4260,20 @@
       <c r="C154" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="E154" s="1" t="s">
-        <v>164</v>
+      <c r="D154" t="s">
+        <v>263</v>
+      </c>
+      <c r="E154" s="1">
+        <v>4</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G154" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A155" s="1">
         <v>154</v>
       </c>
@@ -3784,14 +4283,20 @@
       <c r="C155" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="E155" s="1" t="s">
-        <v>164</v>
+      <c r="D155" t="s">
+        <v>264</v>
+      </c>
+      <c r="E155" s="1">
+        <v>4</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G155" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A156" s="1">
         <v>155</v>
       </c>
@@ -3801,14 +4306,20 @@
       <c r="C156" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="E156" s="1" t="s">
-        <v>164</v>
+      <c r="D156" t="s">
+        <v>265</v>
+      </c>
+      <c r="E156" s="1">
+        <v>5</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G156" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A157" s="1">
         <v>156</v>
       </c>
@@ -3818,14 +4329,20 @@
       <c r="C157" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="E157" s="1" t="s">
-        <v>164</v>
+      <c r="D157" t="s">
+        <v>266</v>
+      </c>
+      <c r="E157" s="1">
+        <v>5</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G157" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A158" s="1">
         <v>157</v>
       </c>
@@ -3835,14 +4352,20 @@
       <c r="C158" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="E158" s="1" t="s">
-        <v>164</v>
+      <c r="D158" t="s">
+        <v>267</v>
+      </c>
+      <c r="E158" s="1">
+        <v>6</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G158" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A159" s="1">
         <v>158</v>
       </c>
@@ -3852,10 +4375,16 @@
       <c r="C159" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="E159" s="1" t="s">
-        <v>164</v>
+      <c r="D159" t="s">
+        <v>268</v>
+      </c>
+      <c r="E159" s="1">
+        <v>6</v>
       </c>
       <c r="F159" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="G159" s="1" t="s">
         <v>164</v>
       </c>
     </row>
